--- a/integrate/template/탬플릿_요구사항명세서.xlsx
+++ b/integrate/template/탬플릿_요구사항명세서.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/secucen/Downloads/project/sample_20260531_template_updated/template/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/secucen/Downloads/project/integrate_20260601/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C716AD10-13E9-1147-9CB7-B211FB34C19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE2F890-736B-2346-B375-BC616DA8897D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="600" windowWidth="22960" windowHeight="13860" tabRatio="609" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41847,18 +41847,18 @@
     <row r="28" spans="2:11" hidden="1"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C3:H3"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="I14:I15"/>
     <mergeCell ref="M3:P3"/>
     <mergeCell ref="Q3:Q4"/>
     <mergeCell ref="R3:R4"/>
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="J14:J15"/>
     <mergeCell ref="K14:K15"/>
-    <mergeCell ref="C3:H3"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="I14:I15"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
